--- a/Hardware/production/positions.xlsx
+++ b/Hardware/production/positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saleh\Desktop\Saleh Uni\sem 7\senior year project\Flight Controller\Hardware\production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA6B7F8-C0D4-4308-8802-3505BC4F6993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E695700F-6AD7-4D21-9AF3-ABCA8536A634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="19200" windowHeight="11170" xr2:uid="{6F0F2AF3-BE7C-4435-8EF3-B97DB954307E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EF06F55D-5B1F-40CB-A247-AAC625F064EC}"/>
   </bookViews>
   <sheets>
     <sheet name="positions" sheetId="1" r:id="rId1"/>
@@ -1392,11 +1392,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF5571C-5D62-44DB-9E1C-A3DF3CCED614}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA64EEC3-A27F-418C-B928-4338AB0E5B9E}">
   <dimension ref="A1:E165"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -1472,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>144.7525</v>
+        <v>144.5575</v>
       </c>
       <c r="C5">
         <v>-91.537499999999994</v>
@@ -1489,7 +1490,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>144.7525</v>
+        <v>144.5575</v>
       </c>
       <c r="C6">
         <v>-92.837500000000006</v>
@@ -1883,7 +1884,7 @@
         <v>122.15</v>
       </c>
       <c r="C29">
-        <v>-110.39</v>
+        <v>-110.14</v>
       </c>
       <c r="D29">
         <v>270</v>
@@ -2036,7 +2037,7 @@
         <v>132.34</v>
       </c>
       <c r="C38">
-        <v>-85.23</v>
+        <v>-85.46</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2053,7 +2054,7 @@
         <v>132.38</v>
       </c>
       <c r="C39">
-        <v>-86.74</v>
+        <v>-86.98</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2104,7 +2105,7 @@
         <v>131.41999999999999</v>
       </c>
       <c r="C42">
-        <v>-88.41</v>
+        <v>-89.17</v>
       </c>
       <c r="D42">
         <v>90</v>
@@ -2121,7 +2122,7 @@
         <v>132.84</v>
       </c>
       <c r="C43">
-        <v>-87.95</v>
+        <v>-88.24</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2696,7 +2697,7 @@
         <v>82</v>
       </c>
       <c r="B77">
-        <v>144.56</v>
+        <v>144.46714600000001</v>
       </c>
       <c r="C77">
         <v>-96.18</v>
@@ -2886,7 +2887,7 @@
         <v>124.14</v>
       </c>
       <c r="C88">
-        <v>-99.65</v>
+        <v>-99.22</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -2903,7 +2904,7 @@
         <v>124.02</v>
       </c>
       <c r="C89">
-        <v>-109.96</v>
+        <v>-109.66</v>
       </c>
       <c r="D89">
         <v>180</v>
@@ -2920,7 +2921,7 @@
         <v>122.17</v>
       </c>
       <c r="C90">
-        <v>-99.24</v>
+        <v>-98.81</v>
       </c>
       <c r="D90">
         <v>90</v>
@@ -2971,7 +2972,7 @@
         <v>130.41999999999999</v>
       </c>
       <c r="C93">
-        <v>-88.39</v>
+        <v>-89.15</v>
       </c>
       <c r="D93">
         <v>270</v>
@@ -4161,7 +4162,7 @@
         <v>124.07</v>
       </c>
       <c r="C163">
-        <v>-104.88500000000001</v>
+        <v>-104.47499999999999</v>
       </c>
       <c r="D163">
         <v>270</v>

--- a/Hardware/production/positions.xlsx
+++ b/Hardware/production/positions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Saleh\Desktop\Saleh Uni\sem 7\senior year project\Flight Controller\Hardware\production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E695700F-6AD7-4D21-9AF3-ABCA8536A634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CA787689-CBA7-4950-B9B6-7A6F23C82261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EF06F55D-5B1F-40CB-A247-AAC625F064EC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{F10E011E-9A7A-4E01-A862-89F291B15E01}"/>
   </bookViews>
   <sheets>
     <sheet name="positions" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="129">
   <si>
     <t>Designator</t>
   </si>
@@ -365,132 +365,6 @@
   </si>
   <si>
     <t>SW2</t>
-  </si>
-  <si>
-    <t>TP1</t>
-  </si>
-  <si>
-    <t>TP10</t>
-  </si>
-  <si>
-    <t>TP12</t>
-  </si>
-  <si>
-    <t>TP13</t>
-  </si>
-  <si>
-    <t>TP14</t>
-  </si>
-  <si>
-    <t>TP15</t>
-  </si>
-  <si>
-    <t>TP16</t>
-  </si>
-  <si>
-    <t>TP17</t>
-  </si>
-  <si>
-    <t>TP18</t>
-  </si>
-  <si>
-    <t>TP2</t>
-  </si>
-  <si>
-    <t>TP20</t>
-  </si>
-  <si>
-    <t>TP21</t>
-  </si>
-  <si>
-    <t>TP22</t>
-  </si>
-  <si>
-    <t>TP23</t>
-  </si>
-  <si>
-    <t>TP24</t>
-  </si>
-  <si>
-    <t>TP25</t>
-  </si>
-  <si>
-    <t>TP26</t>
-  </si>
-  <si>
-    <t>TP27</t>
-  </si>
-  <si>
-    <t>TP28</t>
-  </si>
-  <si>
-    <t>TP29</t>
-  </si>
-  <si>
-    <t>TP3</t>
-  </si>
-  <si>
-    <t>TP30</t>
-  </si>
-  <si>
-    <t>TP31</t>
-  </si>
-  <si>
-    <t>TP32</t>
-  </si>
-  <si>
-    <t>TP33</t>
-  </si>
-  <si>
-    <t>TP34</t>
-  </si>
-  <si>
-    <t>TP35</t>
-  </si>
-  <si>
-    <t>TP36</t>
-  </si>
-  <si>
-    <t>TP37</t>
-  </si>
-  <si>
-    <t>TP38</t>
-  </si>
-  <si>
-    <t>TP39</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>TP40</t>
-  </si>
-  <si>
-    <t>TP41</t>
-  </si>
-  <si>
-    <t>TP42</t>
-  </si>
-  <si>
-    <t>TP43</t>
-  </si>
-  <si>
-    <t>TP45</t>
-  </si>
-  <si>
-    <t>TP5</t>
-  </si>
-  <si>
-    <t>TP6</t>
-  </si>
-  <si>
-    <t>TP7</t>
-  </si>
-  <si>
-    <t>TP8</t>
-  </si>
-  <si>
-    <t>TP9</t>
   </si>
   <si>
     <t>U1</t>
@@ -1392,13 +1266,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA64EEC3-A27F-418C-B928-4338AB0E5B9E}">
-  <dimension ref="A1:E165"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6ECD909-4CB1-4710-A007-3322410D8CC2}">
+  <dimension ref="A1:E123"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.6328125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1439,13 +1309,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>139.53</v>
+        <v>146.63999999999999</v>
       </c>
       <c r="C3">
-        <v>-102.27</v>
+        <v>-102.59</v>
       </c>
       <c r="D3">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1456,7 +1326,7 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>143.09</v>
+        <v>142.59</v>
       </c>
       <c r="C4">
         <v>-99.07</v>
@@ -1473,13 +1343,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>144.5575</v>
+        <v>142.9</v>
       </c>
       <c r="C5">
-        <v>-91.537499999999994</v>
+        <v>-96.82</v>
       </c>
       <c r="D5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -1490,13 +1360,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>144.5575</v>
+        <v>144.19999999999999</v>
       </c>
       <c r="C6">
-        <v>-92.837500000000006</v>
+        <v>-96.82</v>
       </c>
       <c r="D6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -1558,10 +1428,10 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>146.28</v>
+        <v>139.38999999999999</v>
       </c>
       <c r="C10">
-        <v>-101.99</v>
+        <v>-102.74</v>
       </c>
       <c r="D10">
         <v>90</v>
@@ -2068,10 +1938,10 @@
         <v>45</v>
       </c>
       <c r="B40">
-        <v>137.5</v>
+        <v>137.57</v>
       </c>
       <c r="C40">
-        <v>-103.36</v>
+        <v>-103.27</v>
       </c>
       <c r="D40">
         <v>180</v>
@@ -2697,13 +2567,13 @@
         <v>82</v>
       </c>
       <c r="B77">
-        <v>144.46714600000001</v>
+        <v>139.36000000000001</v>
       </c>
       <c r="C77">
-        <v>-96.18</v>
+        <v>-97.93</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E77" t="s">
         <v>6</v>
@@ -3258,16 +3128,16 @@
         <v>115</v>
       </c>
       <c r="B110">
-        <v>132.62</v>
+        <v>138.09</v>
       </c>
       <c r="C110">
-        <v>-113.84</v>
+        <v>-105.8</v>
       </c>
       <c r="D110">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="E110" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -3275,13 +3145,13 @@
         <v>116</v>
       </c>
       <c r="B111">
-        <v>124.45</v>
+        <v>134.82</v>
       </c>
       <c r="C111">
-        <v>-79.215000000000003</v>
+        <v>-86.24</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E111" t="s">
         <v>12</v>
@@ -3292,13 +3162,13 @@
         <v>117</v>
       </c>
       <c r="B112">
-        <v>142.47</v>
+        <v>131.72999999999999</v>
       </c>
       <c r="C112">
-        <v>-79.33</v>
+        <v>-107.77</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E112" t="s">
         <v>12</v>
@@ -3309,16 +3179,16 @@
         <v>118</v>
       </c>
       <c r="B113">
-        <v>136.75</v>
+        <v>137.63999999999999</v>
       </c>
       <c r="C113">
-        <v>-114.5</v>
+        <v>-89.262500000000003</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E113" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
@@ -3326,16 +3196,16 @@
         <v>119</v>
       </c>
       <c r="B114">
-        <v>147.99</v>
+        <v>125.545</v>
       </c>
       <c r="C114">
-        <v>-108.41</v>
+        <v>-88.454999999999998</v>
       </c>
       <c r="D114">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
@@ -3343,10 +3213,10 @@
         <v>120</v>
       </c>
       <c r="B115">
-        <v>144.52000000000001</v>
+        <v>143.63999999999999</v>
       </c>
       <c r="C115">
-        <v>-79.325000000000003</v>
+        <v>-98.46</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -3360,16 +3230,16 @@
         <v>121</v>
       </c>
       <c r="B116">
-        <v>134.77500000000001</v>
+        <v>143.76</v>
       </c>
       <c r="C116">
-        <v>-114.5</v>
+        <v>-101.4575</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E116" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -3377,13 +3247,13 @@
         <v>122</v>
       </c>
       <c r="B117">
-        <v>116.72499999999999</v>
+        <v>142.70750000000001</v>
       </c>
       <c r="C117">
-        <v>-90.72</v>
+        <v>-106.43</v>
       </c>
       <c r="D117">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="E117" t="s">
         <v>12</v>
@@ -3394,10 +3264,10 @@
         <v>123</v>
       </c>
       <c r="B118">
-        <v>114.75</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="C118">
-        <v>-98.76</v>
+        <v>-83.46</v>
       </c>
       <c r="D118">
         <v>90</v>
@@ -3411,13 +3281,13 @@
         <v>124</v>
       </c>
       <c r="B119">
-        <v>144.75</v>
+        <v>131.47999999999999</v>
       </c>
       <c r="C119">
-        <v>-114.485</v>
+        <v>-97.63</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E119" t="s">
         <v>12</v>
@@ -3428,13 +3298,13 @@
         <v>125</v>
       </c>
       <c r="B120">
-        <v>132.77500000000001</v>
+        <v>130.30500000000001</v>
       </c>
       <c r="C120">
-        <v>-114.5</v>
+        <v>-86.54</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E120" t="s">
         <v>12</v>
@@ -3445,16 +3315,16 @@
         <v>126</v>
       </c>
       <c r="B121">
-        <v>128.62</v>
+        <v>124.07</v>
       </c>
       <c r="C121">
-        <v>-113.84</v>
+        <v>-104.47499999999999</v>
       </c>
       <c r="D121">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="E121" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
@@ -3462,13 +3332,13 @@
         <v>127</v>
       </c>
       <c r="B122">
-        <v>114.75</v>
+        <v>119.73</v>
       </c>
       <c r="C122">
-        <v>-104.76</v>
+        <v>-96.38</v>
       </c>
       <c r="D122">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="E122" t="s">
         <v>12</v>
@@ -3479,729 +3349,15 @@
         <v>128</v>
       </c>
       <c r="B123">
-        <v>147.99</v>
+        <v>144.29</v>
       </c>
       <c r="C123">
-        <v>-106.47</v>
+        <v>-88.2</v>
       </c>
       <c r="D123">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="E123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
-        <v>129</v>
-      </c>
-      <c r="B124">
-        <v>130.77500000000001</v>
-      </c>
-      <c r="C124">
-        <v>-114.5</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="E124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125">
-        <v>130.47999999999999</v>
-      </c>
-      <c r="C125">
-        <v>-79.28</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="E125" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
-        <v>131</v>
-      </c>
-      <c r="B126">
-        <v>114.72</v>
-      </c>
-      <c r="C126">
-        <v>-88.65</v>
-      </c>
-      <c r="D126">
-        <v>90</v>
-      </c>
-      <c r="E126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" t="s">
-        <v>132</v>
-      </c>
-      <c r="B127">
-        <v>138.72</v>
-      </c>
-      <c r="C127">
-        <v>-111.88500000000001</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="E127" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" t="s">
-        <v>133</v>
-      </c>
-      <c r="B128">
-        <v>128.49</v>
-      </c>
-      <c r="C128">
-        <v>-79.28</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" t="s">
-        <v>134</v>
-      </c>
-      <c r="B129">
-        <v>126.77500000000001</v>
-      </c>
-      <c r="C129">
-        <v>-114.47499999999999</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-      <c r="E129" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" t="s">
-        <v>135</v>
-      </c>
-      <c r="B130">
-        <v>142.75</v>
-      </c>
-      <c r="C130">
-        <v>-114.5</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-      <c r="E130" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" t="s">
-        <v>136</v>
-      </c>
-      <c r="B131">
-        <v>128.77500000000001</v>
-      </c>
-      <c r="C131">
-        <v>-114.5</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="E131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" t="s">
-        <v>137</v>
-      </c>
-      <c r="B132">
-        <v>136.65</v>
-      </c>
-      <c r="C132">
-        <v>-113.87</v>
-      </c>
-      <c r="D132">
-        <v>180</v>
-      </c>
-      <c r="E132" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" t="s">
-        <v>138</v>
-      </c>
-      <c r="B133">
-        <v>126.52</v>
-      </c>
-      <c r="C133">
-        <v>-81.260000000000005</v>
-      </c>
-      <c r="D133">
-        <v>180</v>
-      </c>
-      <c r="E133" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A134" t="s">
-        <v>139</v>
-      </c>
-      <c r="B134">
-        <v>114.74</v>
-      </c>
-      <c r="C134">
-        <v>-92.71</v>
-      </c>
-      <c r="D134">
-        <v>90</v>
-      </c>
-      <c r="E134" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A135" t="s">
-        <v>140</v>
-      </c>
-      <c r="B135">
-        <v>114.75</v>
-      </c>
-      <c r="C135">
-        <v>-94.71</v>
-      </c>
-      <c r="D135">
-        <v>90</v>
-      </c>
-      <c r="E135" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
-        <v>141</v>
-      </c>
-      <c r="B136">
-        <v>132.47999999999999</v>
-      </c>
-      <c r="C136">
-        <v>-79.305000000000007</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-      <c r="E136" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>142</v>
-      </c>
-      <c r="B137">
-        <v>134.51</v>
-      </c>
-      <c r="C137">
-        <v>-79.290000000000006</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="E137" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>143</v>
-      </c>
-      <c r="B138">
-        <v>138.5</v>
-      </c>
-      <c r="C138">
-        <v>-79.3</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-      <c r="E138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>144</v>
-      </c>
-      <c r="B139">
-        <v>136.5</v>
-      </c>
-      <c r="C139">
-        <v>-79.3</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-      <c r="E139" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>145</v>
-      </c>
-      <c r="B140">
-        <v>138.75</v>
-      </c>
-      <c r="C140">
-        <v>-114.47499999999999</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-      <c r="E140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>146</v>
-      </c>
-      <c r="B141">
-        <v>140.47</v>
-      </c>
-      <c r="C141">
-        <v>-81.319999999999993</v>
-      </c>
-      <c r="D141">
-        <v>180</v>
-      </c>
-      <c r="E141" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>147</v>
-      </c>
-      <c r="B142">
-        <v>140.75</v>
-      </c>
-      <c r="C142">
-        <v>-114.5</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="E142" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>148</v>
-      </c>
-      <c r="B143">
-        <v>114.66500000000001</v>
-      </c>
-      <c r="C143">
-        <v>-102.66</v>
-      </c>
-      <c r="D143">
-        <v>90</v>
-      </c>
-      <c r="E143" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>149</v>
-      </c>
-      <c r="B144">
-        <v>114.75</v>
-      </c>
-      <c r="C144">
-        <v>-100.76</v>
-      </c>
-      <c r="D144">
-        <v>90</v>
-      </c>
-      <c r="E144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>150</v>
-      </c>
-      <c r="B145">
-        <v>134.62</v>
-      </c>
-      <c r="C145">
-        <v>-111.845</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>151</v>
-      </c>
-      <c r="B146">
-        <v>130.63999999999999</v>
-      </c>
-      <c r="C146">
-        <v>-111.83499999999999</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="E146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>152</v>
-      </c>
-      <c r="B147">
-        <v>122.75</v>
-      </c>
-      <c r="C147">
-        <v>-114.5</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>153</v>
-      </c>
-      <c r="B148">
-        <v>114.75</v>
-      </c>
-      <c r="C148">
-        <v>-96.73</v>
-      </c>
-      <c r="D148">
-        <v>90</v>
-      </c>
-      <c r="E148" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>154</v>
-      </c>
-      <c r="B149">
-        <v>116.78</v>
-      </c>
-      <c r="C149">
-        <v>-106.76</v>
-      </c>
-      <c r="D149">
-        <v>270</v>
-      </c>
-      <c r="E149" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>155</v>
-      </c>
-      <c r="B150">
-        <v>122.5</v>
-      </c>
-      <c r="C150">
-        <v>-79.17</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="E150" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>156</v>
-      </c>
-      <c r="B151">
-        <v>124.75</v>
-      </c>
-      <c r="C151">
-        <v>-114.5</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="E151" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>157</v>
-      </c>
-      <c r="B152">
-        <v>138.09</v>
-      </c>
-      <c r="C152">
-        <v>-105.8</v>
-      </c>
-      <c r="D152">
-        <v>90</v>
-      </c>
-      <c r="E152" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>158</v>
-      </c>
-      <c r="B153">
-        <v>134.82</v>
-      </c>
-      <c r="C153">
-        <v>-86.24</v>
-      </c>
-      <c r="D153">
-        <v>90</v>
-      </c>
-      <c r="E153" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>159</v>
-      </c>
-      <c r="B154">
-        <v>131.72999999999999</v>
-      </c>
-      <c r="C154">
-        <v>-107.77</v>
-      </c>
-      <c r="D154">
-        <v>180</v>
-      </c>
-      <c r="E154" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>160</v>
-      </c>
-      <c r="B155">
-        <v>137.63999999999999</v>
-      </c>
-      <c r="C155">
-        <v>-89.262500000000003</v>
-      </c>
-      <c r="D155">
-        <v>270</v>
-      </c>
-      <c r="E155" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>161</v>
-      </c>
-      <c r="B156">
-        <v>125.545</v>
-      </c>
-      <c r="C156">
-        <v>-88.454999999999998</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="E156" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>162</v>
-      </c>
-      <c r="B157">
-        <v>143.63999999999999</v>
-      </c>
-      <c r="C157">
-        <v>-98.46</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="E157" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>163</v>
-      </c>
-      <c r="B158">
-        <v>143.76</v>
-      </c>
-      <c r="C158">
-        <v>-101.4575</v>
-      </c>
-      <c r="D158">
-        <v>180</v>
-      </c>
-      <c r="E158" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>164</v>
-      </c>
-      <c r="B159">
-        <v>142.70750000000001</v>
-      </c>
-      <c r="C159">
-        <v>-106.43</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="E159" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>165</v>
-      </c>
-      <c r="B160">
-        <v>140.80000000000001</v>
-      </c>
-      <c r="C160">
-        <v>-83.46</v>
-      </c>
-      <c r="D160">
-        <v>90</v>
-      </c>
-      <c r="E160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>166</v>
-      </c>
-      <c r="B161">
-        <v>131.47999999999999</v>
-      </c>
-      <c r="C161">
-        <v>-97.63</v>
-      </c>
-      <c r="D161">
-        <v>270</v>
-      </c>
-      <c r="E161" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>167</v>
-      </c>
-      <c r="B162">
-        <v>130.30500000000001</v>
-      </c>
-      <c r="C162">
-        <v>-86.54</v>
-      </c>
-      <c r="D162">
-        <v>180</v>
-      </c>
-      <c r="E162" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>168</v>
-      </c>
-      <c r="B163">
-        <v>124.07</v>
-      </c>
-      <c r="C163">
-        <v>-104.47499999999999</v>
-      </c>
-      <c r="D163">
-        <v>270</v>
-      </c>
-      <c r="E163" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>169</v>
-      </c>
-      <c r="B164">
-        <v>119.73</v>
-      </c>
-      <c r="C164">
-        <v>-96.38</v>
-      </c>
-      <c r="D164">
-        <v>270</v>
-      </c>
-      <c r="E164" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>170</v>
-      </c>
-      <c r="B165">
-        <v>144.29</v>
-      </c>
-      <c r="C165">
-        <v>-88.2</v>
-      </c>
-      <c r="D165">
-        <v>270</v>
-      </c>
-      <c r="E165" t="s">
         <v>6</v>
       </c>
     </row>
